--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10615,34 +10615,34 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
-        <v>8098000</v>
+        <v>7369100</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>23748</v>
+        <v>21610</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="5" t="n">
-        <v>7369180</v>
+        <v>7369100</v>
       </c>
       <c r="L151" s="5" t="n">
         <v>21610</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15581,34 +15581,34 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
-        <v>8638000</v>
+        <v>7860500</v>
       </c>
       <c r="I228" s="5" t="n">
-        <v>21868</v>
+        <v>19900</v>
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K228" s="5" t="n">
-        <v>7860580</v>
+        <v>7860500</v>
       </c>
       <c r="L228" s="5" t="n">
         <v>19900</v>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N228" s="3" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -17162,7 +17162,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -17348,7 +17348,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>86</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18402,7 +18402,7 @@
           <t>B | 338呎 (2房)
 $772万
 $22,831/呎
-(26年-07月-09日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -18474,7 +18474,7 @@
           <t>L | 343呎 (2房)
 $769万
 $22,421/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -18505,7 +18505,7 @@
           <t>B | 338呎 (2房)
 $763万
 $22,567/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -18608,7 +18608,7 @@
           <t>B | 338呎 (2房)
 $760万
 $22,483/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -18711,7 +18711,7 @@
           <t>B | 338呎 (2房)
 $757万
 $22,389/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -18814,7 +18814,7 @@
           <t>B | 338呎 (2房)
 $752万
 $22,254/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -18830,7 +18830,7 @@
           <t>D | 342呎 (2房)
 $805万
 $23,551/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -18894,7 +18894,7 @@
           <t>M | 469呎 (2房)
 $1066万
 $22,721/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -18917,7 +18917,7 @@
           <t>B | 338呎 (2房)
 $765万
 $22,628/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -18941,7 +18941,7 @@
           <t>E | 342呎 (2房)
 $762万
 $22,268/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -19020,7 +19020,7 @@
           <t>B | 338呎 (2房)
 $745万
 $22,031/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -19028,7 +19028,7 @@
           <t>C | 344呎 (2房)
 $757万
 $22,020/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -19044,7 +19044,7 @@
           <t>E | 342呎 (2房)
 $755万
 $22,082/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -19115,7 +19115,7 @@
           <t>A | 585呎 (3房)
 $1280万
 $21,874/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -19123,7 +19123,7 @@
           <t>B | 338呎 (2房)
 $741万
 $21,937/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -19131,7 +19131,7 @@
           <t>C | 344呎 (2房)
 $752万
 $21,848/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -19203,7 +19203,7 @@
           <t>M | 469呎 (2房)
 $1037万
 $22,102/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
           <t>A | 585呎 (3房)
 $1270万
 $21,705/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -19226,7 +19226,7 @@
           <t>B | 338呎 (2房)
 $738万
 $21,824/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -19234,7 +19234,7 @@
           <t>C | 344呎 (2房)
 $746万
 $21,692/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -19298,7 +19298,7 @@
           <t>L | 343呎 (2房)
 $740万
 $21,585/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
@@ -19329,7 +19329,7 @@
           <t>B | 338呎 (2房)
 $733万
 $21,694/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -19337,7 +19337,7 @@
           <t>C | 344呎 (2房)
 $742万
 $21,565/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -19353,7 +19353,7 @@
           <t>E | 342呎 (2房)
 $740万
 $21,635/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -19432,7 +19432,7 @@
           <t>B | 338呎 (2房)
 $730万
 $21,592/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -19440,7 +19440,7 @@
           <t>C | 344呎 (2房)
 $738万
 $21,440/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -19456,7 +19456,7 @@
           <t>E | 342呎 (2房)
 $736万
 $21,513/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -19535,7 +19535,7 @@
           <t>B | 338呎 (2房)
 $725万
 $21,452/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -19543,7 +19543,7 @@
           <t>C | 344呎 (2房)
 $733万
 $21,316/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -19551,7 +19551,7 @@
           <t>D | 342呎 (2房)
 $730万
 $21,337/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -19559,15 +19559,15 @@
           <t>E | 342呎 (2房)
 $732万
 $21,393/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$810万
-$23,748/呎
-(在售)</t>
+$737万
+$21,610/呎
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -19616,7 +19616,7 @@
           <t>A | 585呎 (3房)
 $1244万
 $21,257/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -19624,7 +19624,7 @@
           <t>B | 338呎 (2房)
 $721万
 $21,339/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -19648,7 +19648,7 @@
           <t>E | 342呎 (2房)
 $728万
 $21,300/呎
-(26年-07月-13日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -19656,7 +19656,7 @@
           <t>F | 341呎 (2房)
 $732万
 $21,479/呎
-(26年-06月-30日)</t>
+(26年-07月-29日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -19713,7 +19713,7 @@
           <t>B | 338呎 (2房)
 $719万
 $21,264/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -19721,7 +19721,7 @@
           <t>C | 344呎 (2房)
 $727万
 $21,128/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -19729,7 +19729,7 @@
           <t>D | 342呎 (2房)
 $724万
 $21,175/呎
-(26年-07月-13日)</t>
+(26年-07月-29日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -19737,7 +19737,7 @@
           <t>E | 342呎 (2房)
 $725万
 $21,212/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -19745,7 +19745,7 @@
           <t>F | 341呎 (2房)
 $745万
 $21,840/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -19802,7 +19802,7 @@
           <t>B | 338呎 (2房)
 $716万
 $21,191/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -19810,7 +19810,7 @@
           <t>C | 344呎 (2房)
 $739万
 $21,495/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -19818,7 +19818,7 @@
           <t>D | 342呎 (2房)
 $737万
 $21,548/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -19826,7 +19826,7 @@
           <t>E | 342呎 (2房)
 $738万
 $21,583/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -19891,7 +19891,7 @@
           <t>B | 338呎 (2房)
 $714万
 $21,113/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -19899,7 +19899,7 @@
           <t>C | 344呎 (2房)
 $737万
 $21,414/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -19907,7 +19907,7 @@
           <t>D | 342呎 (2房)
 $718万
 $21,007/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -19915,7 +19915,7 @@
           <t>E | 342呎 (2房)
 $759万
 $22,201/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -19923,7 +19923,7 @@
           <t>F | 341呎 (2房)
 $719万
 $21,074/呎
-(26年-07月-11日)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -19947,7 +19947,7 @@
           <t>J | 395呎 (2房)
 $852万
 $21,572/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="K21" s="24" t="inlineStr"/>
@@ -19980,7 +19980,7 @@
           <t>B | 338呎 (2房)
 $711万
 $21,040/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -19988,7 +19988,7 @@
           <t>C | 344呎 (2房)
 $718万
 $20,880/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -19996,7 +19996,7 @@
           <t>D | 342呎 (2房)
 $755万
 $22,085/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -20004,7 +20004,7 @@
           <t>E | 342呎 (2房)
 $717万
 $20,970/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -20012,7 +20012,7 @@
           <t>F | 341呎 (2房)
 $713万
 $20,911/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -20069,7 +20069,7 @@
           <t>B | 338呎 (2房)
 $709万
 $20,962/呎
-(26年-06月-13日)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -20077,7 +20077,7 @@
           <t>C | 344呎 (2房)
 $716万
 $20,800/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -20085,7 +20085,7 @@
           <t>D | 342呎 (2房)
 $713万
 $20,861/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -20093,7 +20093,7 @@
           <t>E | 342呎 (2房)
 $715万
 $20,898/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -20101,7 +20101,7 @@
           <t>F | 341呎 (2房)
 $748万
 $21,945/呎
-(26年-07月-09日)</t>
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -20125,7 +20125,7 @@
           <t>J | 395呎 (2房)
 $792万
 $20,041/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr"/>
@@ -20135,7 +20135,7 @@
           <t>M | 469呎 (2房)
 $976万
 $20,800/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -20158,7 +20158,7 @@
           <t>B | 338呎 (2房)
 $706万
 $20,884/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -20166,7 +20166,7 @@
           <t>C | 344呎 (2房)
 $713万
 $20,740/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -20174,7 +20174,7 @@
           <t>D | 342呎 (2房)
 $711万
 $20,797/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -20182,7 +20182,7 @@
           <t>E | 342呎 (2房)
 $713万
 $20,834/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -20190,7 +20190,7 @@
           <t>F | 341呎 (2房)
 $721万
 $21,139/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -20239,7 +20239,7 @@
           <t>A | 585呎 (3房)
 $1198万
 $20,477/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -20247,7 +20247,7 @@
           <t>B | 338呎 (2房)
 $740万
 $21,901/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -20255,7 +20255,7 @@
           <t>C | 344呎 (2房)
 $710万
 $20,649/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -20263,7 +20263,7 @@
           <t>D | 342呎 (2房)
 $708万
 $20,714/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -20271,7 +20271,7 @@
           <t>E | 342呎 (2房)
 $710万
 $20,749/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -20298,12 +20298,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
-$864万
-$21,868/呎
-(在售)</t>
+$786万
+$19,900/呎
+(26年-07月-25日)</t>
         </is>
       </c>
       <c r="K25" s="24" t="inlineStr"/>
@@ -20336,7 +20336,7 @@
           <t>B | 338呎 (2房)
 $736万
 $21,785/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -20344,7 +20344,7 @@
           <t>C | 344呎 (2房)
 $706万
 $20,536/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -20352,7 +20352,7 @@
           <t>D | 342呎 (2房)
 $705万
 $20,603/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -20360,7 +20360,7 @@
           <t>E | 342呎 (2房)
 $746万
 $21,813/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -20402,7 +20402,7 @@
           <t>M | 469呎 (2房)
 $956万
 $20,390/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -20425,7 +20425,7 @@
           <t>B | 338呎 (2房)
 $694万
 $20,521/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -20433,7 +20433,7 @@
           <t>C | 344呎 (2房)
 $696万
 $20,231/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -20441,7 +20441,7 @@
           <t>D | 342呎 (2房)
 $700万
 $20,475/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -20449,7 +20449,7 @@
           <t>E | 342呎 (2房)
 $714万
 $20,873/呎
-(26年-07月-04日)</t>
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -20514,7 +20514,7 @@
           <t>B | 338呎 (2房)
 $688万
 $20,357/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -20522,7 +20522,7 @@
           <t>C | 344呎 (2房)
 $703万
 $20,449/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -20538,7 +20538,7 @@
           <t>E | 342呎 (2房)
 $705万
 $20,618/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">

--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -8403,34 +8403,34 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>8211000</v>
+        <v>7472000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>24079</v>
+        <v>21912</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="5" t="n">
-        <v>7472010</v>
+        <v>7472000</v>
       </c>
       <c r="L117" s="5" t="n">
         <v>21912</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -9179,34 +9179,34 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
-        <v>8183000</v>
+        <v>7446500</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>23997</v>
+        <v>21837</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="5" t="n">
-        <v>7446530</v>
+        <v>7446500</v>
       </c>
       <c r="L129" s="5" t="n">
         <v>21837</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
@@ -16225,34 +16225,34 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
-        <v>8563000</v>
+        <v>7792300</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>21678</v>
+        <v>19727</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K238" s="5" t="n">
-        <v>7792330</v>
+        <v>7792300</v>
       </c>
       <c r="L238" s="5" t="n">
         <v>19727</v>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19253,12 +19253,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$821万
-$24,079/呎
-(在售)</t>
+$747万
+$21,912/呎
+(26年-08月-01日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -19356,12 +19356,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$818万
-$23,997/呎
-(在售)</t>
+$745万
+$21,837/呎
+(26年-08月-01日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -20387,12 +20387,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
-$856万
-$21,678/呎
-(在售)</t>
+$779万
+$19,727/呎
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="K26" s="24" t="inlineStr"/>

--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -5528,7 +5528,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -11445,34 +11445,34 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
-        <v>8022000</v>
+        <v>7300000</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>23320</v>
+        <v>21221</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="5" t="n">
-        <v>7300020</v>
+        <v>7300000</v>
       </c>
       <c r="L164" s="5" t="n">
         <v>21221</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N164" s="3" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18814,7 +18814,7 @@
           <t>B | 338呎 (2房)
 $752万
 $22,254/呎
-(26年-07月-15日)</t>
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -19627,12 +19627,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
-$802万
-$23,320/呎
-(在售)</t>
+$730万
+$21,221/呎
+(26年-08月-04日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -19923,7 +19923,7 @@
           <t>F | 341呎 (2房)
 $719万
 $21,074/呎
-(26年-07月-12日)</t>
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">

--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -15586,7 +15586,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -20303,7 +20303,7 @@
           <t>J | 395呎 (2房)
 $786万
 $19,900/呎
-(26年-07月-25日)</t>
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="K25" s="24" t="inlineStr"/>

--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -8408,7 +8408,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8465,34 +8465,34 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>8181000</v>
+        <v>7444700</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>23921</v>
+        <v>21768</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="5" t="n">
-        <v>7444710</v>
+        <v>7444700</v>
       </c>
       <c r="L118" s="5" t="n">
         <v>21768</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19245,12 +19245,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
-$818万
-$23,921/呎
-(在售)</t>
+$744万
+$21,768/呎
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -19258,7 +19258,7 @@
           <t>F | 341呎 (2房)
 $747万
 $21,912/呎
-(26年-08月-01日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -19361,7 +19361,7 @@
           <t>F | 341呎 (2房)
 $745万
 $21,837/呎
-(26年-08月-01日)</t>
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -19567,7 +19567,7 @@
           <t>F | 341呎 (2房)
 $737万
 $21,610/呎
-(26年-07月-23日)</t>
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -20392,7 +20392,7 @@
           <t>J | 395呎 (2房)
 $779万
 $19,727/呎
-(26年-07月-31日)</t>
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="K26" s="24" t="inlineStr"/>

--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -6975,34 +6975,34 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>8285000</v>
+        <v>7705000</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>24225</v>
+        <v>22529</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="5" t="n">
-        <v>7539350</v>
+        <v>7705000</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>22045</v>
+        <v>22529</v>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
@@ -8845,34 +8845,34 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
-        <v>8094000</v>
+        <v>7365500</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>23598</v>
+        <v>21474</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>7365540</v>
+        <v>7365500</v>
       </c>
       <c r="L124" s="5" t="n">
         <v>21474</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -9629,34 +9629,34 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
-        <v>8042000</v>
+        <v>7318200</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>23446</v>
+        <v>21336</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="5" t="n">
-        <v>7318220</v>
+        <v>7318200</v>
       </c>
       <c r="L136" s="5" t="n">
         <v>21336</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N136" s="3" t="inlineStr">
@@ -12555,23 +12555,23 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
-        <v>7960000</v>
+        <v>7243600</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>23343</v>
+        <v>21242</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K181" s="5" t="n">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr">
@@ -16885,34 +16885,34 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
-        <v>8503000</v>
+        <v>7737700</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>21527</v>
+        <v>19589</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>7737730</v>
+        <v>7737700</v>
       </c>
       <c r="L248" s="5" t="n">
         <v>19589</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19031,12 +19031,12 @@
 (26年-07月-10日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
-$828万
-$24,225/呎
-(在售)</t>
+$770万
+$22,529/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -19396,12 +19396,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L15" s="22" t="inlineStr">
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
-$809万
-$23,598/呎
-(在售)</t>
+$737万
+$21,474/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -19499,12 +19499,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L16" s="22" t="inlineStr">
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
-$804万
-$23,446/呎
-(在售)</t>
+$732万
+$21,336/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -19829,12 +19829,12 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$796万
-$23,343/呎
-(在售)</t>
+$724万
+$21,242/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -20476,12 +20476,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J27" s="22" t="inlineStr">
+      <c r="J27" s="21" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
-$850万
-$21,527/呎
-(在售)</t>
+$774万
+$19,589/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="K27" s="24" t="inlineStr"/>

--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -11383,34 +11383,34 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
-        <v>7993000</v>
+        <v>7433400</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>23371</v>
+        <v>21735</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K163" s="5" t="n">
-        <v>7273630</v>
+        <v>7433400</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>21268</v>
+        <v>21735</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N163" s="3" t="inlineStr">
@@ -17879,34 +17879,34 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
-        <v>7641000</v>
+        <v>6953300</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>22342</v>
+        <v>20331</v>
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K263" s="5" t="n">
-        <v>6953310</v>
+        <v>6953300</v>
       </c>
       <c r="L263" s="5" t="n">
         <v>20331</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19635,12 +19635,12 @@
 (26年-08月-04日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
-$799万
-$23,371/呎
-(在售)</t>
+$743万
+$21,735/呎
+(26年-08月-23日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -20525,12 +20525,12 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
-$764万
-$22,342/呎
-(在售)</t>
+$695万
+$20,331/呎
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">

--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -7293,34 +7293,34 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
-        <v>8184000</v>
+        <v>7447400</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>23860</v>
+        <v>21713</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="5" t="n">
-        <v>7447440</v>
+        <v>7447400</v>
       </c>
       <c r="L100" s="5" t="n">
         <v>21713</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -10995,34 +10995,34 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
-        <v>11048000</v>
+        <v>10053600</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>23557</v>
+        <v>21436</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="5" t="n">
-        <v>10053680</v>
+        <v>10053600</v>
       </c>
       <c r="L157" s="5" t="n">
         <v>21436</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
@@ -12283,34 +12283,34 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>10939000</v>
+        <v>9954400</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>23324</v>
+        <v>21225</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>9954490</v>
+        <v>9954400</v>
       </c>
       <c r="L177" s="5" t="n">
         <v>21225</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19190,12 +19190,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
-$818万
-$23,860/呎
-(在售)</t>
+$745万
+$21,713/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -19685,12 +19685,12 @@
       </c>
       <c r="K18" s="24" t="inlineStr"/>
       <c r="L18" s="24" t="inlineStr"/>
-      <c r="M18" s="22" t="inlineStr">
+      <c r="M18" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
-$1105万
-$23,557/呎
-(在售)</t>
+$1005万
+$21,436/呎
+(26年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -19863,12 +19863,12 @@
       </c>
       <c r="K20" s="24" t="inlineStr"/>
       <c r="L20" s="24" t="inlineStr"/>
-      <c r="M20" s="22" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
-$1094万
-$23,324/呎
-(在售)</t>
+$995万
+$21,225/呎
+(26年-08月-25日)</t>
         </is>
       </c>
     </row>

--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -5725,23 +5725,23 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>8240000</v>
+        <v>7498400</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>24023</v>
+        <v>21861</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="5" t="n">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18984,12 +18984,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L11" s="22" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
-$824万
-$24,023/呎
-(在售)</t>
+$750万
+$21,861/呎
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">

--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -127,7 +127,7 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00000000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -277,7 +277,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3387,34 +3387,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H41" s="5" t="n">
+        <v>8447000</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>24991</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>7686770</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>22742</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -4125,34 +4117,34 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>8318000</v>
+        <v>7569300</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>24251</v>
+        <v>22068</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>7569380</v>
+        <v>7569300</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>22068</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -4187,7 +4179,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4195,34 +4187,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H53" s="5" t="n">
+        <v>8411000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>24885</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>7654010</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>22645</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -4793,7 +4777,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4917,7 +4901,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4979,7 +4963,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -4987,34 +4971,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H65" s="5" t="n">
+        <v>8383000</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>24802</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>7628530</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>22570</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -5461,7 +5437,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -5787,7 +5763,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5795,34 +5771,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H77" s="5" t="n">
+        <v>8348000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>24698</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>7596680</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>22475</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -6067,7 +6035,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6191,7 +6159,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6253,7 +6221,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6377,7 +6345,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -6509,7 +6477,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6571,7 +6539,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -6579,34 +6547,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H89" s="5" t="n">
+        <v>8313000</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>24595</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9.00%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>7564800</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>22381</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -6851,7 +6811,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -7355,7 +7315,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7363,34 +7323,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H101" s="5" t="n">
+        <v>8276000</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>24485</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>7531160</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>22282</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -7425,7 +7377,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -7627,7 +7579,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7689,34 +7641,34 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
-        <v>8236000</v>
+        <v>7494700</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>24082</v>
+        <v>21914</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>7494760</v>
+        <v>7494700</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>21915</v>
+        <v>21914</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -7751,7 +7703,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -8123,7 +8075,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -8131,34 +8083,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H113" s="5" t="n">
+        <v>8233000</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>24358</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>7492030</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>22166</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -8527,7 +8471,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -8907,7 +8851,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -8915,34 +8859,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H125" s="5" t="n">
+        <v>8192000</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>24237</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>7454720</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>22055</v>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
@@ -8977,7 +8913,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -9303,34 +9239,34 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
-        <v>8117000</v>
+        <v>7386400</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>23734</v>
+        <v>21598</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="5" t="n">
-        <v>7386470</v>
+        <v>7386400</v>
       </c>
       <c r="L131" s="5" t="n">
         <v>21598</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="3" t="inlineStr">
@@ -9691,7 +9627,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -9699,34 +9635,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H137" s="5" t="n">
+        <v>8141000</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>24086</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>7408310</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>21918</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
@@ -9901,7 +9829,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -9909,34 +9837,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H140" s="5" t="n">
+        <v>8085000</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>23920</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>7357350</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>21767</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N140" s="3" t="inlineStr">
@@ -9971,7 +9891,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -10095,7 +10015,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -10281,7 +10201,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10343,7 +10263,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -10351,34 +10271,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H147" s="5" t="n">
+        <v>11087000</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>23640</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>10089170</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>21512</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N147" s="3" t="inlineStr">
@@ -10413,7 +10325,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -10545,7 +10457,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -10553,34 +10465,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H150" s="5" t="n">
+        <v>8040000</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>23787</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>7316400</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>21646</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -11057,7 +10961,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -11450,7 +11354,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11631,7 +11535,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -11639,34 +11543,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H167" s="5" t="n">
+        <v>11007000</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>23469</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>10016370</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>21357</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N167" s="3" t="inlineStr">
@@ -11701,7 +11597,7 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -12485,7 +12381,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -12493,34 +12389,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H180" s="5" t="n">
+        <v>7902000</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>23379</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>7190820</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>21275</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N180" s="3" t="inlineStr">
@@ -12865,7 +12753,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -13059,7 +12947,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -13067,34 +12955,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H189" s="5" t="n">
+        <v>8758000</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>22456</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>7969780</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>20435</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
@@ -13129,7 +13009,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -13137,34 +13017,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H190" s="5" t="n">
+        <v>7840000</v>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>23195</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>7134400</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>21108</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N190" s="3" t="inlineStr">
@@ -13509,34 +13381,34 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
-        <v>13507000</v>
+        <v>12291300</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>23089</v>
+        <v>21011</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>12291370</v>
+        <v>12291300</v>
       </c>
       <c r="L196" s="5" t="n">
         <v>21011</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -13633,7 +13505,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -13641,34 +13513,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H198" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I198" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H198" s="5" t="n">
+        <v>8806000</v>
+      </c>
+      <c r="I198" s="5" t="n">
+        <v>22294</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K198" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L198" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>8013460</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>20287</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N198" s="3" t="inlineStr">
@@ -13703,7 +13567,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -13711,34 +13575,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I199" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H199" s="5" t="n">
+        <v>8704000</v>
+      </c>
+      <c r="I199" s="5" t="n">
+        <v>22318</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K199" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L199" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>7920640</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>20309</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N199" s="3" t="inlineStr">
@@ -13773,7 +13629,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -13781,34 +13637,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H200" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I200" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H200" s="5" t="n">
+        <v>7779000</v>
+      </c>
+      <c r="I200" s="5" t="n">
+        <v>23015</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K200" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L200" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>7078890</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>20943</v>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N200" s="3" t="inlineStr">
@@ -14228,14 +14076,14 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
-        <v>9755200</v>
+        <v>10291200</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>20800</v>
+        <v>21943</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -14243,10 +14091,10 @@
         </is>
       </c>
       <c r="K207" s="5" t="n">
-        <v>9755200</v>
+        <v>10291200</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>20800</v>
+        <v>21943</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -14347,7 +14195,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -14355,34 +14203,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H209" s="5" t="n">
+        <v>8643000</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>22162</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>7865130</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>20167</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N209" s="3" t="inlineStr">
@@ -14417,7 +14257,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -14425,34 +14265,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H210" s="5" t="n">
+        <v>7724000</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>22852</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>7028840</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>20795</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
@@ -14554,14 +14386,14 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
-        <v>7147100</v>
+        <v>7539800</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>20898</v>
+        <v>22046</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
@@ -14569,10 +14401,10 @@
         </is>
       </c>
       <c r="K212" s="5" t="n">
-        <v>7147100</v>
+        <v>7539800</v>
       </c>
       <c r="L212" s="5" t="n">
-        <v>20898</v>
+        <v>22046</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
@@ -14616,14 +14448,14 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
-        <v>7134400</v>
+        <v>7526400</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>20861</v>
+        <v>22007</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -14631,10 +14463,10 @@
         </is>
       </c>
       <c r="K213" s="5" t="n">
-        <v>7134400</v>
+        <v>7526400</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>20861</v>
+        <v>22007</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
@@ -14797,7 +14629,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -14929,7 +14761,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -14937,34 +14769,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H218" s="5" t="n">
+        <v>8666000</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>21939</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>7886060</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>19965</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
@@ -14999,7 +14823,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -15007,34 +14831,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H219" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I219" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H219" s="5" t="n">
+        <v>8586000</v>
+      </c>
+      <c r="I219" s="5" t="n">
+        <v>22015</v>
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K219" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L219" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>7813260</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>20034</v>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N219" s="3" t="inlineStr">
@@ -15069,7 +14885,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -15077,34 +14893,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H220" s="5" t="n">
+        <v>7680000</v>
+      </c>
+      <c r="I220" s="5" t="n">
+        <v>22722</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>6988800</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>20677</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
@@ -15519,7 +15327,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -15643,7 +15451,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -15651,34 +15459,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H229" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I229" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H229" s="5" t="n">
+        <v>8529000</v>
+      </c>
+      <c r="I229" s="5" t="n">
+        <v>21869</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K229" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L229" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>7761390</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>19901</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">
@@ -15713,7 +15513,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -15721,34 +15521,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H230" s="5" t="n">
+        <v>7642000</v>
+      </c>
+      <c r="I230" s="5" t="n">
+        <v>22609</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>6954220</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>20575</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
@@ -15783,7 +15575,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -15791,34 +15583,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H231" s="5" t="n">
+        <v>7706000</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>22598</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9.00%</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>7012400</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>20564</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -16287,7 +16071,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16295,34 +16079,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H239" s="5" t="n">
+        <v>8461000</v>
+      </c>
+      <c r="I239" s="5" t="n">
+        <v>21695</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>7699510</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>19742</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -16357,7 +16133,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16365,34 +16141,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H240" s="5" t="n">
+        <v>7603000</v>
+      </c>
+      <c r="I240" s="5" t="n">
+        <v>22494</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>6918730</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>20470</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
@@ -16427,7 +16195,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -16435,34 +16203,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H241" s="5" t="n">
+        <v>7646000</v>
+      </c>
+      <c r="I241" s="5" t="n">
+        <v>22422</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>6957860</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>20404</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -16947,7 +16707,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -16955,34 +16715,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H249" s="5" t="n">
+        <v>8393000</v>
+      </c>
+      <c r="I249" s="5" t="n">
+        <v>21521</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>7637630</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>19584</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -17017,7 +16769,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -17025,34 +16777,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H250" s="5" t="n">
+        <v>7528000</v>
+      </c>
+      <c r="I250" s="5" t="n">
+        <v>22272</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>6850480</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>20268</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
@@ -17087,7 +16831,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17095,34 +16839,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H251" s="5" t="n">
+        <v>7577000</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>22220</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>6895070</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>20220</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
@@ -17405,7 +17141,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -17677,7 +17413,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17685,34 +17421,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H260" s="5" t="n">
+        <v>7453000</v>
+      </c>
+      <c r="I260" s="5" t="n">
+        <v>22050</v>
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9.00%</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>6782200</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>20066</v>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
@@ -17747,7 +17475,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -17755,34 +17483,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H261" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I261" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H261" s="5" t="n">
+        <v>7510000</v>
+      </c>
+      <c r="I261" s="5" t="n">
+        <v>22023</v>
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K261" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L261" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>6834100</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>20041</v>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
@@ -18189,27 +17909,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>89</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18217,7 @@
           <t>A | 585呎 (3房)
 $1485万
 $25,390/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -18572,12 +18292,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L7" s="22" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $841万
 $24,507/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -18667,20 +18387,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K8" s="20" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L8" s="22" t="inlineStr">
+$845万
+$24,991/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $836万
 $24,370/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -18698,12 +18418,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1466万
 $25,056/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -18770,20 +18490,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K9" s="20" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L9" s="22" t="inlineStr">
+$841万
+$24,885/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
-$832万
-$24,251/呎
-(在售)</t>
+$757万
+$22,068/呎
+(26年-08月-30日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -18817,12 +18537,12 @@
 (26年-08月-05日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $845万
 $24,552/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -18873,20 +18593,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K10" s="20" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="inlineStr">
+$838万
+$24,802/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $828万
 $24,146/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -18904,12 +18624,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1440万
 $24,612/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -18920,20 +18640,20 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $839万
 $24,401/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $835万
 $24,427/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -18944,12 +18664,12 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $838万
 $24,572/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -18976,12 +18696,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K11" s="20" t="inlineStr">
+      <c r="K11" s="23" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
--
--
-(待售)</t>
+$835万
+$24,698/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -19047,12 +18767,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $832万
 $24,405/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -19079,20 +18799,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L12" s="22" t="inlineStr">
+$831万
+$24,595/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $821万
 $23,939/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -19134,28 +18854,28 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $822万
 $24,038/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
-$824万
-$24,082/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
+$749万
+$21,914/呎
+(26年-08月-30日)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $826万
 $24,220/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -19179,15 +18899,15 @@
           <t>J | 390呎 (2房)
 $939万
 $24,077/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K13" s="20" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
--
--
-(待售)</t>
+$828万
+$24,485/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -19237,12 +18957,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $817万
 $23,877/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -19285,12 +19005,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K14" s="20" t="inlineStr">
+      <c r="K14" s="23" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
--
--
-(待售)</t>
+$823万
+$24,358/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -19340,12 +19060,12 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
-$812万
-$23,734/呎
-(在售)</t>
+$739万
+$21,598/呎
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -19380,20 +19100,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t>J | 390呎 (2房)
 $929万
 $23,810/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K15" s="20" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
--
--
-(待售)</t>
+$819万
+$24,237/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -19419,12 +19139,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1376万
 $23,518/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -19443,12 +19163,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $807万
 $23,602/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -19459,15 +19179,207 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $814万
 $23,883/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+$808万
+$23,920/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+$814万
+$24,086/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$732万
+$21,336/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$725万
+$21,452/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$733万
+$21,316/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$730万
+$21,337/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$732万
+$21,393/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$737万
+$21,610/呎
+(26年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+$804万
+$23,787/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$916万
+$23,187/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="K17" s="24" t="inlineStr"/>
+      <c r="L17" s="24" t="inlineStr"/>
+      <c r="M17" s="23" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1109万
+$23,640/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1244万
+$21,257/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$721万
+$21,339/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$730万
+$21,221/呎
+(26年-08月-31日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$743万
+$21,735/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$728万
+$21,300/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$732万
+$21,479/呎
+(26年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
 -
@@ -19475,7 +19387,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 -
@@ -19483,31 +19395,284 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$910万
+$23,051/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="K18" s="24" t="inlineStr"/>
+      <c r="L18" s="24" t="inlineStr"/>
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1005万
+$21,436/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$719万
+$21,264/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$727万
+$21,128/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$724万
+$21,175/呎
+(26年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$725万
+$21,212/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$745万
+$21,840/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$732万
-$21,336/呎
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$905万
+$22,919/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="K19" s="24" t="inlineStr"/>
+      <c r="L19" s="24" t="inlineStr"/>
+      <c r="M19" s="23" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1101万
+$23,469/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1357万
+$23,190/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$716万
+$21,191/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$739万
+$21,495/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$737万
+$21,548/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$738万
+$21,583/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$724万
+$21,242/呎
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="M16" s="20" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+$790万
+$23,379/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K20" s="24" t="inlineStr"/>
+      <c r="L20" s="24" t="inlineStr"/>
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$995万
+$21,225/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1229万
+$21,011/呎
+(26年-08月-30日)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$714万
+$21,113/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$737万
+$21,414/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$718万
+$21,007/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$759万
+$22,201/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$719万
+$21,074/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+$784万
+$23,195/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+$876万
+$22,456/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$852万
+$21,572/呎
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="K21" s="24" t="inlineStr"/>
+      <c r="L21" s="24" t="inlineStr"/>
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 -
@@ -19516,13 +19681,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 -
@@ -19530,73 +19695,251 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
-$725万
-$21,452/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
+$711万
+$21,040/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
-$733万
-$21,316/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
+$718万
+$20,880/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
-$730万
-$21,337/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
+$755万
+$22,085/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
-$732万
-$21,393/呎
+$717万
+$20,970/呎
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$737万
-$21,610/呎
-(26年-08月-18日)</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
+$713万
+$20,911/呎
+(26年-07月-22日)</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
+$778万
+$23,015/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+$870万
+$22,318/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$881万
+$22,294/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr"/>
+      <c r="L22" s="24" t="inlineStr"/>
+      <c r="M22" s="23" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1079万
+$23,002/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1335万
+$22,824/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$709万
+$20,962/呎
+(26年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$716万
+$20,800/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$753万
+$22,007/呎
+(26年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$754万
+$22,046/呎
+(26年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$748万
+$21,945/呎
+(26年-07月-30日)</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+$772万
+$22,852/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+$864万
+$22,162/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$792万
+$20,041/呎
+(26年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="K23" s="24" t="inlineStr"/>
+      <c r="L23" s="24" t="inlineStr"/>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1029万
+$21,943/呎
+(26年-06月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$706万
+$20,884/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$713万
+$20,740/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$711万
+$20,797/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$713万
+$20,834/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$721万
+$21,139/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+$768万
+$22,722/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="22" t="inlineStr">
+$859万
+$22,015/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
-$916万
-$23,187/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K17" s="24" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr"/>
-      <c r="M17" s="20" t="inlineStr">
+$867万
+$21,939/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K24" s="24" t="inlineStr"/>
+      <c r="L24" s="24" t="inlineStr"/>
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 -
@@ -19605,102 +19948,102 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
-$1244万
-$21,257/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
+$1198万
+$20,477/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
-$721万
-$21,339/呎
+$740万
+$21,901/呎
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
-$730万
-$21,221/呎
-(26年-08月-04日)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
+$710万
+$20,649/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
-$743万
-$21,735/呎
-(26年-08月-23日)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
+$708万
+$20,714/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
-$728万
-$21,300/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
+$710万
+$20,749/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$732万
-$21,479/呎
-(26年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
+$771万
+$22,598/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
+$764万
+$22,609/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="inlineStr">
+$853万
+$21,869/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
-$910万
-$23,051/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K18" s="24" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr"/>
-      <c r="M18" s="21" t="inlineStr">
+$786万
+$19,900/呎
+(26年-08月-12日)</t>
+        </is>
+      </c>
+      <c r="K25" s="24" t="inlineStr"/>
+      <c r="L25" s="24" t="inlineStr"/>
+      <c r="M25" s="23" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
-$1005万
-$21,436/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
+$1060万
+$22,591/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 -
@@ -19708,73 +20051,162 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
-$719万
-$21,264/呎
+$736万
+$21,785/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$706万
+$20,536/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$705万
+$20,603/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$746万
+$21,813/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$765万
+$22,422/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+$760万
+$22,494/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+$846万
+$21,695/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$779万
+$19,727/呎
+(26年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="inlineStr"/>
+      <c r="L26" s="24" t="inlineStr"/>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$956万
+$20,390/呎
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1300万
+$22,226/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$694万
+$20,521/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
-$727万
-$21,128/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+$696万
+$20,231/呎
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
-$724万
-$21,175/呎
-(26年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+$700万
+$20,475/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
-$725万
-$21,212/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+$714万
+$20,873/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$745万
-$21,840/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
+$758万
+$22,220/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
+$753万
+$22,272/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="inlineStr">
+$839万
+$21,521/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
-$905万
-$22,919/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K19" s="24" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr"/>
-      <c r="M19" s="20" t="inlineStr">
+$774万
+$19,589/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr"/>
+      <c r="L27" s="24" t="inlineStr"/>
+      <c r="M27" s="20" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 -
@@ -19783,191 +20215,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1357万
-$23,190/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$716万
-$21,191/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$739万
-$21,495/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$737万
-$21,548/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$738万
-$21,583/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$724万
-$21,242/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K20" s="24" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr"/>
-      <c r="M20" s="21" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$995万
-$21,225/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1351万
-$23,089/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$714万
-$21,113/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$737万
-$21,414/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$718万
-$21,007/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$759万
-$22,201/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$719万
-$21,074/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="20" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="21" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$852万
-$21,572/呎
-(26年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="K21" s="24" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr"/>
-      <c r="M21" s="20" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 -
@@ -19975,540 +20229,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$711万
-$21,040/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$718万
-$20,880/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$755万
-$22,085/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$717万
-$20,970/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$713万
-$20,911/呎
-(26年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K22" s="24" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr"/>
-      <c r="M22" s="23" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$1079万
-$23,002/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1335万
-$22,824/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$709万
-$20,962/呎
-(26年-06月-14日)</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$716万
-$20,800/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$713万
-$20,861/呎
-(26年-07月-23日)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$715万
-$20,898/呎
-(26年-07月-23日)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$748万
-$21,945/呎
-(26年-07月-30日)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="21" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$792万
-$20,041/呎
-(26年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="K23" s="24" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr"/>
-      <c r="M23" s="21" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$976万
-$20,800/呎
-(26年-07月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$706万
-$20,884/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$713万
-$20,740/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$711万
-$20,797/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$713万
-$20,834/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$721万
-$21,139/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K24" s="24" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr"/>
-      <c r="M24" s="20" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1198万
-$20,477/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$740万
-$21,901/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$710万
-$20,649/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$708万
-$20,714/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$710万
-$20,749/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$786万
-$19,900/呎
-(26年-08月-12日)</t>
-        </is>
-      </c>
-      <c r="K25" s="24" t="inlineStr"/>
-      <c r="L25" s="24" t="inlineStr"/>
-      <c r="M25" s="22" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$1060万
-$22,591/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$736万
-$21,785/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$706万
-$20,536/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$705万
-$20,603/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$746万
-$21,813/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$779万
-$19,727/呎
-(26年-08月-18日)</t>
-        </is>
-      </c>
-      <c r="K26" s="24" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr"/>
-      <c r="M26" s="21" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$956万
-$20,390/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1300万
-$22,226/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$694万
-$20,521/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$696万
-$20,231/呎
-(26年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$700万
-$20,475/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$714万
-$20,873/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$774万
-$19,589/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="K27" s="24" t="inlineStr"/>
-      <c r="L27" s="24" t="inlineStr"/>
-      <c r="M27" s="20" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
@@ -20541,20 +20261,20 @@
 (26年-07月-20日)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
+$751万
+$22,023/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
--
--
-(待售)</t>
+$745万
+$22,050/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">

--- a/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第4期/首岸第4期_销控明细表.xlsx
@@ -8414,7 +8414,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -18970,7 +18970,7 @@
           <t>E | 342呎 (2房)
 $744万
 $21,768/呎
-(26年-08月-14日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
